--- a/ReportLab.Console/Exports/Syncfusion/Export_HR Skyddsrond_ Region Mitt - 2026_Syncfusion_Excel_Corporate.xlsx
+++ b/ReportLab.Console/Exports/Syncfusion/Export_HR Skyddsrond_ Region Mitt - 2026_Syncfusion_Excel_Corporate.xlsx
@@ -1114,7 +1114,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Du0J1ub8bO4VL658PVOn2bsM9icYZ7uhU/OKDO3AjbRy/bcV3Roq4sdhVMutlYsJn7ZQjoHbclIn4ZlLhsrtvw==" saltValue="5SHJ9rdsF7LviGCAFxCx4A==" spinCount="500" sheet="1" objects="1" scenarios="1" pivotTables="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="FS+ooOeNR3EJHHw3qxGrqC8VTZzzkTmVQuMEeN+b8Pxq8nbZKJwW/aPscFKhCDeUq5VQHL1qjYu4G1F2+cMaKg==" saltValue="Qqf95WB2dl9LY/8pv4n5dg==" spinCount="500" sheet="1" objects="1" scenarios="1" pivotTables="1"/>
   <mergeCells count="1">
     <mergeCell ref="A10:S10"/>
   </mergeCells>
